--- a/tb/catalogo_TB.xlsx
+++ b/tb/catalogo_TB.xlsx
@@ -562,7 +562,8 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>DR-TB treatment, care and support - Procurement of TB medicines (PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance + PSM Costs - QA/QC + PSM Costs - Customs Clearance)</t>
+          <t>DR-TB treatment, care and support - Procurement of TB medicines (PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance + PSM Costs - QA/QC + PSM Costs - Customs Clearance)
+[PT] Tratamento, cuidados e apoio à DR-TB - Aquisição de medicamentos para TB (PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -639,8 +640,8 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DR-TB diagnosis/drug susceptibility testing (DST) - (Procurement of Molecular testing reagents, test kits and consumables + Procurement of Consumables + Contracts for Maintenance and Services + PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance + PSM Costs - QA/QC + PSM Costs - Customs Clearance)
-</t>
+          <t>DR-TB diagnosis/drug susceptibility testing (DST) - (Procurement of Molecular testing reagents, test kits and consumables + Procurement of Consumables + Contracts for Maintenance and Services + PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance + PSM Costs - QA/QC + PSM Costs - Customs Clearance)
+[PT] Diagnóstico de DR-TB/Teste de sensibilidade aos fármacos (DST) - (Aquisição de reagentes para testes moleculares, kits de teste e consumíveis + Aquisição de Consumíveis + Contratos de Manutenção e Serviços + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -717,7 +718,8 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>KVP - People in prisons/jails/detention centers: (Procurement of TB medicines +Procurement of Laboratory reagents, test kits and consumables + Contracts for Maintenance and Services + PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance + PSM Costs - Customs Clearance + PSM Costs - QA/QC+others)</t>
+          <t>KVP - People in prisons/jails/detention centers: (Procurement of TB medicines +Procurement of Laboratory reagents, test kits and consumables + Contracts for Maintenance and Services + PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance + PSM Costs - Customs Clearance + PSM Costs - QA/QC+others)
+[PT] KVP - Pessoas em prisões/cadeias/centros de detenção: (Aquisição de medicamentos para TB + Aquisição de reagentes laboratoriais, kits de teste e consumíveis + Contratos de Manutenção e Serviços + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Desalfandegamento + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + outros)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -794,7 +796,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>KVP - Miners and mining communities: (Procurement of TB medicines + Procurement of Laboratory reagents, test kits and consumables + Contracts for Maintenance and Services + PSM Costs - PSA fees + PSM Costs - Customs Clearance + PSM Costs - QA/QC)</t>
+          <t>KVP - Miners and mining communities: (Procurement of TB medicines + Procurement of Laboratory reagents, test kits and consumables + Contracts for Maintenance and Services + PSM Costs - PSA fees + PSM Costs - Customs Clearance + PSM Costs - QA/QC)
+[PT] KVP - Mineiros e comunidades mineiras: (Aquisição de medicamentos para TB + Aquisição de reagentes laboratoriais, kits de teste e consumíveis + Contratos de Manutenção e Serviços + PSM Costs - Taxas PSA + PSM Costs - Desalfandegamento + PSM Costs - Controlo de Qualidade/Garantia de Qualidade)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -871,7 +874,8 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>KVP - Children and adolescents: (Procurement of TB medicines+Procurement of Laboratory reagents, test kits and consumables+Contracts for Maintenance and Services+PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance)</t>
+          <t>KVP - Children and adolescents: (Procurement of TB medicines+Procurement of Laboratory reagents, test kits and consumables+Contracts for Maintenance and Services+PSM Costs - PSA fees + PSM Costs - Freight &amp; Insurance)
+[PT] KVP - Crianças e adolescentes: (Aquisição de medicamentos para TB + Aquisição de reagentes laboratoriais, kits de teste e consumíveis + Contratos de Manutenção e Serviços + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -948,7 +952,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>TB screening and diagnosis: (Procurement of Molecular testing reagents, test kits and consumables+Procurement of Laboratory reagents, test kits and consumables+Procurement of Consumables+Contracts for Maintenance and Services+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)</t>
+          <t>TB screening and diagnosis: (Procurement of Molecular testing reagents, test kits and consumables+Procurement of Laboratory reagents, test kits and consumables+Procurement of Consumables+Contracts for Maintenance and Services+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)
+[PT] Rastreio e diagnóstico de TB: (Aquisição de reagentes para testes moleculares, kits de teste e consumíveis + Aquisição de reagentes laboratoriais, kits de teste e consumíveis + Aquisição de Consumíveis + Contratos de Manutenção e Serviços + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1025,7 +1030,8 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>TB treatment, care and support: (PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)</t>
+          <t>TB treatment, care and support: (PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)
+[PT] Tratamento, cuidados e apoio à TB: (PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1102,7 +1108,8 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Preventive treatment: (Procurement of TB medicines+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)</t>
+          <t>Preventive treatment: (Procurement of TB medicines+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)
+[PT] Tratamento preventivo: (Aquisição de medicamentos para TB + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1179,7 +1186,8 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Infection prevention and control (IPC): (Procurement of PPE+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)</t>
+          <t>Infection prevention and control (IPC): (Procurement of PPE+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)
+[PT] Prevenção e controlo de infecções (IPC): (Aquisição de PPE + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1256,7 +1264,8 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>TB/HIV - Treatment and care: (Procurement of TB medicines+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance+PSM Costs - Customs Clearance)</t>
+          <t>TB/HIV - Treatment and care: (Procurement of TB medicines+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance+PSM Costs - Customs Clearance)
+[PT] TB/HIV - Tratamento e cuidados: (Aquisição de medicamentos para TB + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1331,7 +1340,8 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>TB/HIV - Screening, testing and diagnosis: (Procurement of Laboratory reagents, test kits and consumables+Contracts for Maintenance and Services+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)</t>
+          <t>TB/HIV - Screening, testing and diagnosis: (Procurement of Laboratory reagents, test kits and consumables+Contracts for Maintenance and Services+PSM Costs - PSA fees+PSM Costs - Freight &amp; Insurance+PSM Costs - QA/QC+PSM Costs - Customs Clearance)
+[PT] TB/HIV - Rastreio, testagem e diagnóstico: (Aquisição de reagentes laboratoriais, kits de teste e consumíveis + Contratos de Manutenção e Serviços + PSM Costs - Taxas PSA + PSM Costs - Frete e Seguro + PSM Costs - Controlo de Qualidade/Garantia de Qualidade + PSM Costs - Desalfandegamento)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1408,7 +1418,8 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>TB Screen and diagnosis: CHW intitial trining and refreshment;cellphone, Tablets acquisition for implementer staff; cellphone voucher; Monthly cough days, Mobile clinics, Monthly Transport subsidy;Kyit for implementer staff; Support to Centro de Excelencia de TB;  GeneXpert IT Material (printing Machines, batteries, UPS),  priting an reproduction, radio spots dissimination</t>
+          <t>TB Screen and diagnosis: CHW intitial trining and refreshment;cellphone, Tablets acquisition for implementer staff; cellphone voucher; Monthly cough days, Mobile clinics, Monthly Transport subsidy;Kyit for implementer staff; Support to Centro de Excelencia de TB;  GeneXpert IT Material (printing Machines, batteries, UPS),  priting an reproduction, radio spots dissimination
+[PT] Rastreio e diagnóstico de TB: Formação inicial e de actualização de CHW; aquisição de telemóveis e tablets para o pessoal dos implementadores; vouchers para telemóveis; Dias mensais da tosse, Clínicas móveis, Subsídio mensal de transporte; Kit para o pessoal dos implementadores; Apoio ao Centro de Excelência de TB; Material informático GeneXpert (impressoras, baterias, UPS), impressão e reprodução, divulgação de spots de rádio</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1486,7 +1497,8 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>TB treatment, care and support: Cash incentive subsidy for Pediatric Patients</t>
+          <t>TB treatment, care and support: Cash incentive subsidy for Pediatric Patients
+[PT] Tratamento, cuidados e apoio à TB: Subsídio de incentivo monetário para Pacientes Pediátricos</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1563,7 +1575,8 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>DR-TB  treatment care and support: sputum collection and material, Motorbike for district supervisor; bicicle to support actvities; Technical support and supervision, cash incentive for DR-TB Patients</t>
+          <t>DR-TB  treatment care and support: sputum collection and material, Motorbike for district supervisor; bicicle to support actvities; Technical support and supervision, cash incentive for DR-TB Patients
+[PT] Tratamento, cuidados e apoio à DR-TB: recolha de expectoração e material, Motociclo para supervisor distrital; bicicleta para apoio às actividades; Assistência técnica e supervisão, incentivo monetário para pacientes com DR-TB</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
